--- a/ExelData/Ranged_Weapon_Balancing.xlsx
+++ b/ExelData/Ranged_Weapon_Balancing.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Rimworld'!$A$1:$T$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ratkin'!$A$1:$T$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Ratkin'!$A$1:$T$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Core'!$A$1:$T$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Biotech'!$A$1:$T$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Anomaly'!$A$1:$T$3</definedName>
@@ -2573,7 +2573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2584,7 +2584,7 @@
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
     <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -2595,7 +2595,7 @@
     <col width="12" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
-    <col width="37" customWidth="1" min="20" max="20"/>
+    <col width="33" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3175,13 +3175,13 @@
         <v>0.017</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>0.9</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>13.9</v>
+        <v>10.9</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>5</v>
@@ -3190,13 +3190,13 @@
         <v>0.45</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>14.4</v>
+        <v>13.14</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>12.21</v>
+        <v>11.17</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.848</v>
+        <v>0.85</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0.85</v>
@@ -3211,16 +3211,16 @@
         <v>0.55</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>12.24</v>
+        <v>11.17</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>12.24</v>
+        <v>11.17</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>9.359999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="S9" s="3" t="n">
-        <v>7.92</v>
+        <v>7.23</v>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
@@ -3297,73 +3297,73 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>RK_PrototypePulseRifle</t>
+          <t>RK_Weapon_BFR</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.167</v>
+        <v>0.25</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>31</v>
+        <v>44.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>7.58</v>
+        <v>5</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>5.59</v>
+        <v>3.16</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.6317</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.85</v>
+        <v>0.35</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0.65</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.45</v>
+        <v>0.85</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>5.68</v>
+        <v>3.25</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>6.44</v>
+        <v>1.75</v>
       </c>
       <c r="R11" s="3" t="n">
-        <v>4.93</v>
+        <v>3.25</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>3.41</v>
+        <v>4.25</v>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>Bullet_RK_PrototypePulseRifleLight</t>
+          <t>Bullet_BFR_AP</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>RK_Weapon_BFR</t>
+          <t>RK_Weapon_RatHolicGun</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -3373,127 +3373,61 @@
         <v>0.25</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>44.9</v>
+        <v>30.9</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>5.6</v>
+        <v>2.33</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>3.54</v>
+        <v>0.55</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.6317</v>
+        <v>0.2352</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.65</v>
+        <v>0.2</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.65</v>
+        <v>0.25</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.85</v>
+        <v>0.18</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>3.64</v>
+        <v>0.47</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>1.96</v>
+        <v>0.58</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>3.64</v>
+        <v>0.58</v>
       </c>
       <c r="S12" s="3" t="n">
-        <v>4.76</v>
+        <v>0.42</v>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>Bullet_BFR_AP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>RK_Weapon_RatHolicGun</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="G13" s="3" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0.2352</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N13" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O13" s="4" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="P13" s="3" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="Q13" s="3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="R13" s="3" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="S13" s="3" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
           <t>RK_Bullet_RatHolicGun</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T13"/>
+  <autoFilter ref="A1:T12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
